--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,7 +621,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/hl7-at-patientidentifier</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0203</t>
   </si>
   <si>
     <t>Identifier.type</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedEncounterLGF</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedEncounterLGF</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedEncounter</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedEncounter</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -464,7 +464,7 @@
     <t>Unfalldatum</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-unfalldatum}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-unfalldatum}
 </t>
   </si>
   <si>
@@ -1107,7 +1107,7 @@
     <t>Behandlungsart</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-behandlungsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-behandlungsart-valueset</t>
   </si>
   <si>
     <t>Encounter.class:Behandlungsart.id</t>
@@ -1185,7 +1185,7 @@
     <t>Aufnahmeart2</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-aufnahmeart2-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-aufnahmeart2-valueset</t>
   </si>
   <si>
     <t>Encounter.class:Aufnahmeart2.id</t>
@@ -1432,7 +1432,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedOrganizationAbteilung)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung)
 </t>
   </si>
   <si>
@@ -1869,7 +1869,7 @@
     <t>Encounter.reason:Ursache.value</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-ursache-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-ursache-valueset</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -1943,7 +1943,7 @@
     <t>Encounter.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://example.org/StructureDefinition/MopedAccount)
+    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedAccount)
 </t>
   </si>
   <si>
@@ -2066,7 +2066,7 @@
     <t>aufnahmeart</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-aufnahmeart}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-aufnahmeart}
 </t>
   </si>
   <si>
@@ -2082,7 +2082,7 @@
     <t>transportart</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-transportart}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-transportart}
 </t>
   </si>
   <si>
@@ -2182,7 +2182,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>http://example.org/ValueSet/moped-entlassungsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/moped-entlassungsart-valueset</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -2613,7 +2613,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.57421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -17435,7 +17435,7 @@
         <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1107,7 +1107,7 @@
     <t>Behandlungsart</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-behandlungsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Behandlungsart</t>
   </si>
   <si>
     <t>Encounter.class:Behandlungsart.id</t>
@@ -1146,7 +1146,7 @@
     <t>Encounter.class.coding.system</t>
   </si>
   <si>
-    <t>http://tbd.at/MOPED-encounter-behandlungsart</t>
+    <t>https://elga.moped.at/CodeSystem/BehandlungsartCS</t>
   </si>
   <si>
     <t>Encounter.class:Behandlungsart.coding.version</t>
@@ -1185,7 +1185,7 @@
     <t>Aufnahmeart2</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-aufnahmeart2-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Aufnahmeart2</t>
   </si>
   <si>
     <t>Encounter.class:Aufnahmeart2.id</t>
@@ -1206,7 +1206,7 @@
     <t>Encounter.class:Aufnahmeart2.coding.system</t>
   </si>
   <si>
-    <t>http://tbd.at/moped-ext-aufnahmeart2</t>
+    <t>https://elga.moped.at/CodeSystem/Aufnahmeart2CS</t>
   </si>
   <si>
     <t>Encounter.class:Aufnahmeart2.coding.version</t>
@@ -1258,6 +1258,14 @@
   </si>
   <si>
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://elga.moped.at/CodeSystem/MopedEncounterTypesCS"/&gt;
+    &lt;code value="ENC"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>A specific code indicating type of service provided</t>
@@ -1430,10 +1438,6 @@
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://elga.moped.at/StructureDefinition/MopedOrganizationAbteilung)
-</t>
   </si>
   <si>
     <t>The organization (facility) responsible for this encounter</t>
@@ -1869,7 +1873,7 @@
     <t>Encounter.reason:Ursache.value</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-ursache-valueset</t>
+    <t>https://elga.moped.at/ValueSet/UrsacheValueSet</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -2182,7 +2186,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://elga.moped.at/ValueSet/moped-entlassungsart-valueset</t>
+    <t>https://elga.moped.at/ValueSet/Entlassungsart</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -2613,7 +2617,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="95.89453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.28125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -11687,7 +11691,7 @@
         <v>20</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>20</v>
+        <v>404</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>20</v>
@@ -11705,10 +11709,10 @@
         <v>395</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -11741,24 +11745,24 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11781,13 +11785,13 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11817,10 +11821,10 @@
         <v>395</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -11838,7 +11842,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11853,7 +11857,7 @@
         <v>100</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>20</v>
@@ -11862,19 +11866,19 @@
         <v>170</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11893,16 +11897,16 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11952,7 +11956,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11967,24 +11971,24 @@
         <v>100</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12010,13 +12014,13 @@
         <v>189</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12045,10 +12049,10 @@
         <v>395</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
@@ -12066,7 +12070,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12095,10 +12099,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12121,13 +12125,13 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12178,7 +12182,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12196,25 +12200,25 @@
         <v>20</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>170</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12233,13 +12237,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12290,7 +12294,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12305,13 +12309,13 @@
         <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>20</v>
@@ -12319,10 +12323,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12345,13 +12349,13 @@
         <v>20</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12402,7 +12406,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12431,10 +12435,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12457,16 +12461,16 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12516,7 +12520,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12531,13 +12535,13 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>20</v>
@@ -12545,10 +12549,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12571,7 +12575,7 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>458</v>
+        <v>300</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>459</v>
@@ -12628,7 +12632,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13551,7 +13555,7 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>20</v>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:47:03+00:00</t>
+    <t>2025-03-01T14:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1935,10 +1935,10 @@
     <t>Role that this diagnosis has within the encounter (e.g. admission, billing, discharge …).</t>
   </si>
   <si>
-    <t>Code für den Typ der LKF Diagnose, der angibt ob es sich um eine Haupt- oder Nebendiagnose handelt</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/ValueSet/lkf-diagnose-typ</t>
+    <t>The type of diagnosis this condition represents.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-diagnosis-use</t>
   </si>
   <si>
     <t>DG1-6 (Diagnosis Type)</t>
@@ -2616,7 +2616,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.89453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="23.6484375" customWidth="true" bestFit="true"/>
@@ -17372,7 +17372,7 @@
         <v>20</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>112</v>
+        <v>344</v>
       </c>
       <c r="Y130" t="s" s="2">
         <v>612</v>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedEncounterLGF.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
